--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484046_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484046_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. ALIAGA CHECA</t>
+          <t>M. BENITO MULLERAT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0203</v>
+        <v>2.9783</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9131</v>
+        <v>1.2683</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1073</v>
+        <v>1.7099</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1659</v>
+        <v>4.4228</v>
       </c>
       <c r="H2" t="n">
-        <v>0.57</v>
+        <v>2.1919</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4042</v>
+        <v>2.2309</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5381</v>
+        <v>4.9019</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0978</v>
+        <v>2.9691</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5597</v>
+        <v>1.9329</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3723</v>
+        <v>-0.4791</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5278</v>
+        <v>-0.7772</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1555</v>
+        <v>0.2981</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9838</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-3.1741</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9838</v>
+        <v>2.579</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.59</v>
+        <v>-0.9948</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6177</v>
+        <v>-0.7254</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0277</v>
+        <v>-0.2694</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4607</v>
+        <v>0.1453</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9926</v>
+        <v>0.266</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.532</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BALTÀ CASTELLTORT</t>
+          <t>M. ALIAGA CHECA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9578</v>
+        <v>2.2151</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1052</v>
+        <v>2.3042</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1473</v>
+        <v>-0.0891</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1315</v>
+        <v>0.1659</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9022</v>
+        <v>0.57</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2294</v>
+        <v>-0.4042</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3006</v>
+        <v>1.5381</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2203</v>
+        <v>2.0978</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0803</v>
+        <v>-0.5597</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1691</v>
+        <v>-1.3723</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3181</v>
+        <v>-1.5278</v>
       </c>
       <c r="O3" t="n">
-        <v>0.149</v>
+        <v>0.1555</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5871</v>
+        <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3781</v>
+        <v>-0.3953</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7369</v>
+        <v>-0.2266</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3589</v>
+        <v>-0.1687</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9405</v>
+        <v>0.4607</v>
       </c>
       <c r="W3" t="n">
-        <v>0.266</v>
+        <v>0.9926</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2065</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. BENITO MULLERAT</t>
+          <t>A. BALTÀ CASTELLTORT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7137</v>
+        <v>1.4423</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5088</v>
+        <v>1.6177</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2049</v>
+        <v>-0.1754</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4228</v>
+        <v>1.1315</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1919</v>
+        <v>0.9022</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2309</v>
+        <v>0.2294</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9019</v>
+        <v>1.3006</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9691</v>
+        <v>1.2203</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9329</v>
+        <v>0.0803</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4791</v>
+        <v>-0.1691</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7772</v>
+        <v>-0.3181</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2981</v>
+        <v>0.149</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5952</v>
+        <v>1.3887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1741</v>
+        <v>-0.1984</v>
       </c>
       <c r="R4" t="n">
-        <v>2.579</v>
+        <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.2593</v>
+        <v>-0.1375</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4849</v>
+        <v>0.2495</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7743</v>
+        <v>-0.3869</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1453</v>
+        <v>-0.9405</v>
       </c>
       <c r="W4" t="n">
         <v>0.266</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1206</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2643</v>
+        <v>0.9707</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3149</v>
+        <v>-0.4963</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5792</v>
+        <v>1.467</v>
       </c>
       <c r="G5" t="n">
         <v>1.3354</v>
@@ -844,13 +844,13 @@
         <v>2.1822</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1236</v>
+        <v>-0.17</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3742</v>
+        <v>0.1928</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2506</v>
+        <v>-0.3629</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1947</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1759</v>
+        <v>-1.0348</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9637</v>
+        <v>-0.8787</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2122</v>
+        <v>-0.1561</v>
       </c>
       <c r="G6" t="n">
         <v>-2.2794</v>
@@ -922,13 +922,13 @@
         <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.637</v>
+        <v>-0.4959</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8671</v>
+        <v>-0.7821</v>
       </c>
       <c r="U6" t="n">
-        <v>0.23</v>
+        <v>0.2862</v>
       </c>
       <c r="V6" t="n">
         <v>0.7486</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8473</v>
+        <v>-1.5823</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9162</v>
+        <v>-0.7916</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.931</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-3.1222</v>
@@ -1000,13 +1000,13 @@
         <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.2536</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.255</v>
+        <v>-0.1303</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2636</v>
+        <v>-0.1233</v>
       </c>
       <c r="V7" t="n">
         <v>0.6032</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7577</v>
+        <v>-2.7274</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4285</v>
+        <v>-2.2018</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3292</v>
+        <v>-0.5256</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4948</v>
@@ -1078,13 +1078,13 @@
         <v>1.1903</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3407</v>
+        <v>-0.3103</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.7708</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6569</v>
+        <v>0.4605</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1206</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5132</v>
+        <v>-3.391</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.1496</v>
+        <v>-3.7188</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6364</v>
+        <v>0.3278</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4644</v>
@@ -1156,13 +1156,13 @@
         <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>0.395</v>
+        <v>0.5172</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5611</v>
+        <v>-0.1303</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.6475</v>
       </c>
       <c r="V9" t="n">
         <v>-0.0713</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8705</v>
+        <v>-3.5939</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3398</v>
+        <v>-2.1754</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5308</v>
+        <v>-1.4185</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0029</v>
@@ -1234,13 +1234,13 @@
         <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9454</v>
+        <v>-0.6688</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7481</v>
+        <v>-0.5838</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1973</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1206</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8919</v>
+        <v>-3.8185</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0468</v>
+        <v>-4.0015</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1549</v>
+        <v>0.183</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4126</v>
@@ -1312,13 +1312,13 @@
         <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7635</v>
+        <v>-0.6901</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.68</v>
+        <v>-0.6347</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0834</v>
+        <v>-0.0554</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7239</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.1004</v>
+        <v>-8.541499999999997</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.6324</v>
+        <v>-9.073900000000002</v>
       </c>
       <c r="F12" t="n">
         <v>0.5322</v>
@@ -1390,13 +1390,13 @@
         <v>16.8625</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.1578</v>
+        <v>-3.5991</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.1003</v>
+        <v>-3.5417</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.05739999999999995</v>
+        <v>-0.05739999999999982</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2138000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8863</v>
+        <v>5.2035</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8728</v>
+        <v>3.587</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0135</v>
+        <v>1.6165</v>
       </c>
       <c r="G13" t="n">
         <v>4.1779</v>
@@ -1468,13 +1468,13 @@
         <v>1.5871</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0413</v>
+        <v>0.3584</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8105</v>
+        <v>-0.0963</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8517</v>
+        <v>0.4547</v>
       </c>
       <c r="V13" t="n">
         <v>1.0639</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.19</v>
+        <v>4.7419</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3868</v>
+        <v>1.999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8032</v>
+        <v>2.7429</v>
       </c>
       <c r="G14" t="n">
         <v>1.383</v>
@@ -1546,13 +1546,13 @@
         <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6682</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9125</v>
+        <v>-0.3003</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5807</v>
+        <v>1.5203</v>
       </c>
       <c r="V14" t="n">
         <v>1.5437</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. PARADEDA VIDAL</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8547</v>
+        <v>3.6271</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4101</v>
+        <v>2.2598</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4446</v>
+        <v>1.3673</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4106</v>
+        <v>4.247</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3559</v>
+        <v>1.7233</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0547</v>
+        <v>2.5237</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6338</v>
+        <v>4.0735</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8708</v>
+        <v>2.3791</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7631</v>
+        <v>1.6944</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2233</v>
+        <v>0.1735</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5148</v>
+        <v>-0.6558</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2916</v>
+        <v>0.8292</v>
       </c>
       <c r="P15" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.9919</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-0.9919</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.9838</v>
-      </c>
       <c r="S15" t="n">
-        <v>1.3927</v>
+        <v>0.904</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5022</v>
+        <v>0.1701</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1095</v>
+        <v>0.7339</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9405</v>
+        <v>-0.532</v>
       </c>
       <c r="W15" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2065</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>E. PARADEDA VIDAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4452</v>
+        <v>3.325</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1578</v>
+        <v>2.4918</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2874</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>4.247</v>
+        <v>2.4106</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7233</v>
+        <v>1.3559</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5237</v>
+        <v>1.0547</v>
       </c>
       <c r="J16" t="n">
-        <v>4.0735</v>
+        <v>2.6338</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3791</v>
+        <v>1.8708</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6944</v>
+        <v>0.7631</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1735</v>
+        <v>-0.2233</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6558</v>
+        <v>-0.5148</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8292</v>
+        <v>0.2916</v>
       </c>
       <c r="P16" t="n">
+        <v>0.9919</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.9919</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-1.9838</v>
-      </c>
       <c r="R16" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7221</v>
+        <v>0.863</v>
       </c>
       <c r="T16" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.5839</v>
       </c>
       <c r="U16" t="n">
-        <v>0.654</v>
+        <v>0.279</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.532</v>
+        <v>-0.9405</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.532</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9807</v>
+        <v>2.8368</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4634</v>
+        <v>1.3733</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4442</v>
+        <v>1.4635</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6266</v>
+        <v>-0.4631</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2171</v>
+        <v>0.2717</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4095</v>
+        <v>-0.7348</v>
       </c>
       <c r="J17" t="n">
-        <v>0.832</v>
+        <v>0.1781</v>
       </c>
       <c r="K17" t="n">
-        <v>0.591</v>
+        <v>0.5242</v>
       </c>
       <c r="L17" t="n">
-        <v>0.241</v>
+        <v>-0.3461</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2054</v>
+        <v>-0.6412</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3739</v>
+        <v>-0.2525</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1685</v>
+        <v>-0.3886</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7855</v>
+        <v>1.9838</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9677</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1822</v>
+        <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8023</v>
+        <v>0.3755</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6723</v>
+        <v>-0.0112</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1301</v>
+        <v>0.3868</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3373</v>
+        <v>0.9405</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3373</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7579</v>
+        <v>1.3334</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6591</v>
+        <v>-0.2367</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0988</v>
+        <v>1.5701</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4631</v>
+        <v>-0.0925</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2717</v>
+        <v>1.4311</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7348</v>
+        <v>-1.5236</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1781</v>
+        <v>0.1487</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5242</v>
+        <v>0.746</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3461</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6412</v>
+        <v>-0.2412</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2525</v>
+        <v>0.6851</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3886</v>
+        <v>-0.9263</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9838</v>
+        <v>0.9919</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9838</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7034</v>
+        <v>0.3628</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7254</v>
+        <v>-0.3854</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0221</v>
+        <v>0.7481</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9405</v>
+        <v>0.0713</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.266</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.007</v>
+        <v>0.7343</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3388</v>
+        <v>-2.7898</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3457</v>
+        <v>3.5241</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0925</v>
+        <v>0.6266</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4311</v>
+        <v>0.2171</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5236</v>
+        <v>0.4095</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1487</v>
+        <v>0.832</v>
       </c>
       <c r="K19" t="n">
-        <v>0.746</v>
+        <v>0.591</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5973000000000001</v>
+        <v>0.241</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2412</v>
+        <v>-0.2054</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6851</v>
+        <v>-0.3739</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9263</v>
+        <v>0.1685</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9919</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.9677</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9919</v>
+        <v>2.1822</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0363</v>
+        <v>1.5559</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4874</v>
+        <v>0.3459</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5237000000000001</v>
+        <v>1.21</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0713</v>
+        <v>0.3373</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0713</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="20">
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4073</v>
+        <v>-2.5041</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6697</v>
+        <v>-1.5521</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7376</v>
+        <v>-0.9519</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3984</v>
+        <v>-0.1083</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5395</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8589</v>
+        <v>-0.0427</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5394</v>
+        <v>1.0131</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0605</v>
+        <v>0.9327</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5999</v>
+        <v>0.0803</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.859</v>
+        <v>-1.1213</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6</v>
+        <v>-0.9983</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2591</v>
+        <v>-0.123</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3968</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7891</v>
+        <v>-0.4832</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8616</v>
+        <v>-0.1927</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0726</v>
+        <v>-0.2905</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4012</v>
+        <v>0.0713</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4012</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0065</v>
+        <v>-3.0093</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8582</v>
+        <v>-1.3839</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1483</v>
+        <v>-1.6254</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1083</v>
+        <v>-1.3984</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.5395</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0427</v>
+        <v>-0.8589</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0131</v>
+        <v>-0.5394</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9327</v>
+        <v>0.0605</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0803</v>
+        <v>-0.5999</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1213</v>
+        <v>-0.859</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9983</v>
+        <v>-0.6</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.123</v>
+        <v>-0.2591</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9838</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9857</v>
+        <v>0.1871</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4988</v>
+        <v>0.1474</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4869</v>
+        <v>0.0396</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0713</v>
+        <v>-1.4012</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.532</v>
+        <v>-1.4012</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.806</v>
+        <v>-5.7065</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.6886</v>
+        <v>-6.2805</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.574</v>
       </c>
       <c r="G23" t="n">
         <v>-5.0621</v>
@@ -2248,13 +2248,13 @@
         <v>1.7855</v>
       </c>
       <c r="S23" t="n">
-        <v>0.395</v>
+        <v>0.4945</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6121</v>
+        <v>-0.204</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0071</v>
+        <v>0.6985</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9405</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>10.1004</v>
+        <v>10.7805</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5321000000000007</v>
+        <v>-0.5320999999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>10.6325</v>
+        <v>11.3127</v>
       </c>
       <c r="G24" t="n">
         <v>5.7207</v>
@@ -2308,7 +2308,7 @@
         <v>2.493200000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-5.6744</v>
+        <v>-5.674399999999999</v>
       </c>
       <c r="N24" t="n">
         <v>-3.8613</v>
@@ -2317,7 +2317,7 @@
         <v>-1.813</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9920000000000003</v>
+        <v>-0.9920000000000005</v>
       </c>
       <c r="Q24" t="n">
         <v>-16.8625</v>
@@ -2326,13 +2326,13 @@
         <v>15.8707</v>
       </c>
       <c r="S24" t="n">
-        <v>5.1579</v>
+        <v>5.838</v>
       </c>
       <c r="T24" t="n">
-        <v>0.05750000000000011</v>
+        <v>0.05739999999999998</v>
       </c>
       <c r="U24" t="n">
-        <v>5.1004</v>
+        <v>5.780400000000001</v>
       </c>
       <c r="V24" t="n">
         <v>0.2137999999999999</v>
